--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$40</f>
+              <f>'OssDsign'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$40</f>
+              <f>'OssDsign'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$40</f>
+              <f>'OssDsign'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$40</f>
+              <f>'OssDsign'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$40</f>
+              <f>'Smart Eye'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$40</f>
+              <f>'Smart Eye'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$40</f>
+              <f>'Smart Eye'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$40</f>
+              <f>'Smart Eye'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$40</f>
+              <f>'Integrum'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$40</f>
+              <f>'Integrum'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$40</f>
+              <f>'Integrum'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$40</f>
+              <f>'Integrum'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1676,6 +1676,23 @@
       </c>
       <c r="D40" s="2">
         <f>B40+C40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2822</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>676</v>
+      </c>
+      <c r="D41" s="2">
+        <f>B41+C41</f>
         <v/>
       </c>
     </row>
@@ -1691,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2382,6 +2399,23 @@
       </c>
       <c r="D40" s="2">
         <f>B40+C40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>13828</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>7263</v>
+      </c>
+      <c r="D41" s="2">
+        <f>B41+C41</f>
         <v/>
       </c>
     </row>
@@ -2397,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3091,6 +3125,23 @@
         <v/>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2477</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="D41" s="2">
+        <f>B41+C41</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$41</f>
+              <f>'OssDsign'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$41</f>
+              <f>'OssDsign'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$41</f>
+              <f>'OssDsign'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$41</f>
+              <f>'OssDsign'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$41</f>
+              <f>'Smart Eye'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$41</f>
+              <f>'Smart Eye'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$41</f>
+              <f>'Smart Eye'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$41</f>
+              <f>'Smart Eye'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$41</f>
+              <f>'Integrum'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$41</f>
+              <f>'Integrum'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$41</f>
+              <f>'Integrum'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$41</f>
+              <f>'Integrum'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,23 @@
       </c>
       <c r="D41" s="2">
         <f>B41+C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2822</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="D42" s="2">
+        <f>B42+C42</f>
         <v/>
       </c>
     </row>
@@ -1708,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2416,6 +2433,23 @@
       </c>
       <c r="D41" s="2">
         <f>B41+C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>13828</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>7265</v>
+      </c>
+      <c r="D42" s="2">
+        <f>B42+C42</f>
         <v/>
       </c>
     </row>
@@ -2431,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3142,6 +3176,23 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2477</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D42" s="2">
+        <f>B42+C42</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$42</f>
+              <f>'OssDsign'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$42</f>
+              <f>'OssDsign'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$42</f>
+              <f>'OssDsign'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$42</f>
+              <f>'OssDsign'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$42</f>
+              <f>'Smart Eye'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$42</f>
+              <f>'Smart Eye'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$42</f>
+              <f>'Smart Eye'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$42</f>
+              <f>'Smart Eye'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$42</f>
+              <f>'Integrum'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$42</f>
+              <f>'Integrum'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$42</f>
+              <f>'Integrum'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$42</f>
+              <f>'Integrum'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1710,6 +1710,23 @@
       </c>
       <c r="D42" s="2">
         <f>B42+C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2820</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="D43" s="2">
+        <f>B43+C43</f>
         <v/>
       </c>
     </row>
@@ -1725,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2450,6 +2467,23 @@
       </c>
       <c r="D42" s="2">
         <f>B42+C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>13781</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>7250</v>
+      </c>
+      <c r="D43" s="2">
+        <f>B43+C43</f>
         <v/>
       </c>
     </row>
@@ -2465,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3193,6 +3227,23 @@
         <v/>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2478</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D43" s="2">
+        <f>B43+C43</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$43</f>
+              <f>'OssDsign'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$43</f>
+              <f>'OssDsign'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$43</f>
+              <f>'OssDsign'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$43</f>
+              <f>'OssDsign'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$43</f>
+              <f>'Smart Eye'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$43</f>
+              <f>'Smart Eye'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$43</f>
+              <f>'Smart Eye'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$43</f>
+              <f>'Smart Eye'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$43</f>
+              <f>'Integrum'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$43</f>
+              <f>'Integrum'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$43</f>
+              <f>'Integrum'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$43</f>
+              <f>'Integrum'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1727,6 +1727,23 @@
       </c>
       <c r="D43" s="2">
         <f>B43+C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2817</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="D44" s="2">
+        <f>B44+C44</f>
         <v/>
       </c>
     </row>
@@ -1742,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2484,6 +2501,23 @@
       </c>
       <c r="D43" s="2">
         <f>B43+C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>13737</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>7232</v>
+      </c>
+      <c r="D44" s="2">
+        <f>B44+C44</f>
         <v/>
       </c>
     </row>
@@ -2499,7 +2533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3244,6 +3278,23 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2477</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D44" s="2">
+        <f>B44+C44</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$44</f>
+              <f>'OssDsign'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$44</f>
+              <f>'OssDsign'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$44</f>
+              <f>'OssDsign'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$44</f>
+              <f>'OssDsign'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$44</f>
+              <f>'Smart Eye'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$44</f>
+              <f>'Smart Eye'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$44</f>
+              <f>'Smart Eye'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$44</f>
+              <f>'Smart Eye'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$44</f>
+              <f>'Integrum'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$44</f>
+              <f>'Integrum'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$44</f>
+              <f>'Integrum'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$44</f>
+              <f>'Integrum'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1744,6 +1744,23 @@
       </c>
       <c r="D44" s="2">
         <f>B44+C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2816</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="D45" s="2">
+        <f>B45+C45</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2518,6 +2535,23 @@
       </c>
       <c r="D44" s="2">
         <f>B44+C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>13711</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>7214</v>
+      </c>
+      <c r="D45" s="2">
+        <f>B45+C45</f>
         <v/>
       </c>
     </row>
@@ -2533,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3295,6 +3329,23 @@
         <v/>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2476</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D45" s="2">
+        <f>B45+C45</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$45</f>
+              <f>'OssDsign'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$45</f>
+              <f>'OssDsign'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$45</f>
+              <f>'OssDsign'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$45</f>
+              <f>'OssDsign'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$45</f>
+              <f>'Smart Eye'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$45</f>
+              <f>'Smart Eye'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$45</f>
+              <f>'Smart Eye'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$45</f>
+              <f>'Smart Eye'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$45</f>
+              <f>'Integrum'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$45</f>
+              <f>'Integrum'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$45</f>
+              <f>'Integrum'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$45</f>
+              <f>'Integrum'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,23 @@
       </c>
       <c r="D45" s="2">
         <f>B45+C45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2812</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D46" s="2">
+        <f>B46+C46</f>
         <v/>
       </c>
     </row>
@@ -1776,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2552,6 +2569,23 @@
       </c>
       <c r="D45" s="2">
         <f>B45+C45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>13687</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>7192</v>
+      </c>
+      <c r="D46" s="2">
+        <f>B46+C46</f>
         <v/>
       </c>
     </row>
@@ -2567,7 +2601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3346,6 +3380,23 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2481</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D46" s="2">
+        <f>B46+C46</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$46</f>
+              <f>'OssDsign'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$46</f>
+              <f>'OssDsign'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$46</f>
+              <f>'OssDsign'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$46</f>
+              <f>'OssDsign'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$46</f>
+              <f>'Smart Eye'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$46</f>
+              <f>'Smart Eye'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$46</f>
+              <f>'Smart Eye'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$46</f>
+              <f>'Smart Eye'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$46</f>
+              <f>'Integrum'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$46</f>
+              <f>'Integrum'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$46</f>
+              <f>'Integrum'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$46</f>
+              <f>'Integrum'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1778,6 +1778,23 @@
       </c>
       <c r="D46" s="2">
         <f>B46+C46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2811</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D47" s="2">
+        <f>B47+C47</f>
         <v/>
       </c>
     </row>
@@ -1793,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2586,6 +2603,23 @@
       </c>
       <c r="D46" s="2">
         <f>B46+C46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>13682</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>7192</v>
+      </c>
+      <c r="D47" s="2">
+        <f>B47+C47</f>
         <v/>
       </c>
     </row>
@@ -2601,7 +2635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3397,6 +3431,23 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2493</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D47" s="2">
+        <f>B47+C47</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$47</f>
+              <f>'OssDsign'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$47</f>
+              <f>'OssDsign'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$47</f>
+              <f>'OssDsign'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$47</f>
+              <f>'OssDsign'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$47</f>
+              <f>'Smart Eye'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$47</f>
+              <f>'Smart Eye'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$47</f>
+              <f>'Smart Eye'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$47</f>
+              <f>'Smart Eye'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$47</f>
+              <f>'Integrum'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$47</f>
+              <f>'Integrum'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$47</f>
+              <f>'Integrum'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$47</f>
+              <f>'Integrum'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1795,6 +1795,23 @@
       </c>
       <c r="D47" s="2">
         <f>B47+C47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2811</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D48" s="2">
+        <f>B48+C48</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2620,6 +2637,23 @@
       </c>
       <c r="D47" s="2">
         <f>B47+C47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>13682</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>7192</v>
+      </c>
+      <c r="D48" s="2">
+        <f>B48+C48</f>
         <v/>
       </c>
     </row>
@@ -2635,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3448,6 +3482,23 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2493</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D48" s="2">
+        <f>B48+C48</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$48</f>
+              <f>'OssDsign'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$48</f>
+              <f>'OssDsign'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$48</f>
+              <f>'OssDsign'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$48</f>
+              <f>'OssDsign'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$48</f>
+              <f>'Smart Eye'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$48</f>
+              <f>'Smart Eye'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$48</f>
+              <f>'Smart Eye'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$48</f>
+              <f>'Smart Eye'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$48</f>
+              <f>'Integrum'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$48</f>
+              <f>'Integrum'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$48</f>
+              <f>'Integrum'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$48</f>
+              <f>'Integrum'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1812,6 +1812,23 @@
       </c>
       <c r="D48" s="2">
         <f>B48+C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2811</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="D49" s="2">
+        <f>B49+C49</f>
         <v/>
       </c>
     </row>
@@ -1827,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2654,6 +2671,23 @@
       </c>
       <c r="D48" s="2">
         <f>B48+C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>13682</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>7171</v>
+      </c>
+      <c r="D49" s="2">
+        <f>B49+C49</f>
         <v/>
       </c>
     </row>
@@ -2669,7 +2703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3499,6 +3533,23 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2493</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D49" s="2">
+        <f>B49+C49</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$49</f>
+              <f>'OssDsign'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$49</f>
+              <f>'OssDsign'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$49</f>
+              <f>'OssDsign'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$49</f>
+              <f>'OssDsign'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$49</f>
+              <f>'Smart Eye'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$49</f>
+              <f>'Smart Eye'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$49</f>
+              <f>'Smart Eye'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$49</f>
+              <f>'Smart Eye'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$49</f>
+              <f>'Integrum'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$49</f>
+              <f>'Integrum'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$49</f>
+              <f>'Integrum'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$49</f>
+              <f>'Integrum'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1829,6 +1829,23 @@
       </c>
       <c r="D49" s="2">
         <f>B49+C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2806</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="D50" s="2">
+        <f>B50+C50</f>
         <v/>
       </c>
     </row>
@@ -1844,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2705,23 @@
       </c>
       <c r="D49" s="2">
         <f>B49+C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>13637</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>7145</v>
+      </c>
+      <c r="D50" s="2">
+        <f>B50+C50</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3550,6 +3584,23 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D50" s="2">
+        <f>B50+C50</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$50</f>
+              <f>'OssDsign'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$50</f>
+              <f>'OssDsign'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$50</f>
+              <f>'OssDsign'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$50</f>
+              <f>'OssDsign'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$50</f>
+              <f>'Smart Eye'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$50</f>
+              <f>'Smart Eye'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$50</f>
+              <f>'Smart Eye'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$50</f>
+              <f>'Smart Eye'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$50</f>
+              <f>'Integrum'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$50</f>
+              <f>'Integrum'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$50</f>
+              <f>'Integrum'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$50</f>
+              <f>'Integrum'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1846,6 +1846,23 @@
       </c>
       <c r="D50" s="2">
         <f>B50+C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2798</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D51" s="2">
+        <f>B51+C51</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2722,6 +2739,23 @@
       </c>
       <c r="D50" s="2">
         <f>B50+C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>13594</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="D51" s="2">
+        <f>B51+C51</f>
         <v/>
       </c>
     </row>
@@ -2737,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3601,6 +3635,23 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="D51" s="2">
+        <f>B51+C51</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$51</f>
+              <f>'OssDsign'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$51</f>
+              <f>'OssDsign'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$51</f>
+              <f>'OssDsign'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$51</f>
+              <f>'OssDsign'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$51</f>
+              <f>'Smart Eye'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$51</f>
+              <f>'Smart Eye'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$51</f>
+              <f>'Smart Eye'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$51</f>
+              <f>'Smart Eye'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$51</f>
+              <f>'Integrum'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$51</f>
+              <f>'Integrum'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$51</f>
+              <f>'Integrum'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$51</f>
+              <f>'Integrum'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1863,6 +1863,23 @@
       </c>
       <c r="D51" s="2">
         <f>B51+C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2799</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>675</v>
+      </c>
+      <c r="D52" s="2">
+        <f>B52+C52</f>
         <v/>
       </c>
     </row>
@@ -1878,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2756,6 +2773,23 @@
       </c>
       <c r="D51" s="2">
         <f>B51+C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>13597</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>7120</v>
+      </c>
+      <c r="D52" s="2">
+        <f>B52+C52</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3652,6 +3686,23 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D52" s="2">
+        <f>B52+C52</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$52</f>
+              <f>'OssDsign'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$52</f>
+              <f>'OssDsign'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$52</f>
+              <f>'OssDsign'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$52</f>
+              <f>'OssDsign'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$52</f>
+              <f>'Smart Eye'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$52</f>
+              <f>'Smart Eye'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$52</f>
+              <f>'Smart Eye'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$52</f>
+              <f>'Smart Eye'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$52</f>
+              <f>'Integrum'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$52</f>
+              <f>'Integrum'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$52</f>
+              <f>'Integrum'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$52</f>
+              <f>'Integrum'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1880,6 +1880,23 @@
       </c>
       <c r="D52" s="2">
         <f>B52+C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2798</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D53" s="2">
+        <f>B53+C53</f>
         <v/>
       </c>
     </row>
@@ -1895,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2790,6 +2807,23 @@
       </c>
       <c r="D52" s="2">
         <f>B52+C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>13582</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>7118</v>
+      </c>
+      <c r="D53" s="2">
+        <f>B53+C53</f>
         <v/>
       </c>
     </row>
@@ -2805,7 +2839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3703,6 +3737,23 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D53" s="2">
+        <f>B53+C53</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$53</f>
+              <f>'OssDsign'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$53</f>
+              <f>'OssDsign'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$53</f>
+              <f>'OssDsign'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$53</f>
+              <f>'OssDsign'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$53</f>
+              <f>'Smart Eye'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$53</f>
+              <f>'Smart Eye'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$53</f>
+              <f>'Smart Eye'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$53</f>
+              <f>'Smart Eye'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$53</f>
+              <f>'Integrum'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$53</f>
+              <f>'Integrum'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$53</f>
+              <f>'Integrum'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$53</f>
+              <f>'Integrum'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1897,6 +1897,23 @@
       </c>
       <c r="D53" s="2">
         <f>B53+C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2797</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D54" s="2">
+        <f>B54+C54</f>
         <v/>
       </c>
     </row>
@@ -1912,7 +1929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2824,6 +2841,23 @@
       </c>
       <c r="D53" s="2">
         <f>B53+C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>13584</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>7118</v>
+      </c>
+      <c r="D54" s="2">
+        <f>B54+C54</f>
         <v/>
       </c>
     </row>
@@ -2839,7 +2873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3754,6 +3788,23 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D54" s="2">
+        <f>B54+C54</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$54</f>
+              <f>'OssDsign'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$54</f>
+              <f>'OssDsign'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$54</f>
+              <f>'OssDsign'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$54</f>
+              <f>'OssDsign'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$54</f>
+              <f>'Smart Eye'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$54</f>
+              <f>'Smart Eye'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$54</f>
+              <f>'Smart Eye'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$54</f>
+              <f>'Smart Eye'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$54</f>
+              <f>'Integrum'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$54</f>
+              <f>'Integrum'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$54</f>
+              <f>'Integrum'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$54</f>
+              <f>'Integrum'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1914,6 +1914,23 @@
       </c>
       <c r="D54" s="2">
         <f>B54+C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2797</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="D55" s="2">
+        <f>B55+C55</f>
         <v/>
       </c>
     </row>
@@ -1929,7 +1946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2858,6 +2875,23 @@
       </c>
       <c r="D54" s="2">
         <f>B54+C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>13584</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>7118</v>
+      </c>
+      <c r="D55" s="2">
+        <f>B55+C55</f>
         <v/>
       </c>
     </row>
@@ -2873,7 +2907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3805,6 +3839,23 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D55" s="2">
+        <f>B55+C55</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$55</f>
+              <f>'OssDsign'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$55</f>
+              <f>'OssDsign'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$55</f>
+              <f>'OssDsign'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$55</f>
+              <f>'OssDsign'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$55</f>
+              <f>'Smart Eye'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$55</f>
+              <f>'Smart Eye'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$55</f>
+              <f>'Smart Eye'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$55</f>
+              <f>'Smart Eye'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$55</f>
+              <f>'Integrum'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$55</f>
+              <f>'Integrum'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$55</f>
+              <f>'Integrum'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$55</f>
+              <f>'Integrum'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1931,6 +1931,23 @@
       </c>
       <c r="D55" s="2">
         <f>B55+C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2797</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="D56" s="2">
+        <f>B56+C56</f>
         <v/>
       </c>
     </row>
@@ -1946,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2892,6 +2909,23 @@
       </c>
       <c r="D55" s="2">
         <f>B55+C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>13584</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>7106</v>
+      </c>
+      <c r="D56" s="2">
+        <f>B56+C56</f>
         <v/>
       </c>
     </row>
@@ -2907,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3856,6 +3890,23 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D56" s="2">
+        <f>B56+C56</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$56</f>
+              <f>'OssDsign'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$56</f>
+              <f>'OssDsign'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$56</f>
+              <f>'OssDsign'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$56</f>
+              <f>'OssDsign'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$56</f>
+              <f>'Smart Eye'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$56</f>
+              <f>'Smart Eye'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$56</f>
+              <f>'Smart Eye'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$56</f>
+              <f>'Smart Eye'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$56</f>
+              <f>'Integrum'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$56</f>
+              <f>'Integrum'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$56</f>
+              <f>'Integrum'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$56</f>
+              <f>'Integrum'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1948,6 +1948,23 @@
       </c>
       <c r="D56" s="2">
         <f>B56+C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2797</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>672</v>
+      </c>
+      <c r="D57" s="2">
+        <f>B57+C57</f>
         <v/>
       </c>
     </row>
@@ -1963,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2926,6 +2943,23 @@
       </c>
       <c r="D56" s="2">
         <f>B56+C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>13564</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>7090</v>
+      </c>
+      <c r="D57" s="2">
+        <f>B57+C57</f>
         <v/>
       </c>
     </row>
@@ -2941,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3907,6 +3941,23 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D57" s="2">
+        <f>B57+C57</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$57</f>
+              <f>'OssDsign'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$57</f>
+              <f>'OssDsign'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$57</f>
+              <f>'OssDsign'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$57</f>
+              <f>'OssDsign'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$57</f>
+              <f>'Smart Eye'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$57</f>
+              <f>'Smart Eye'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$57</f>
+              <f>'Smart Eye'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$57</f>
+              <f>'Smart Eye'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$57</f>
+              <f>'Integrum'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$57</f>
+              <f>'Integrum'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$57</f>
+              <f>'Integrum'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$57</f>
+              <f>'Integrum'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1965,6 +1965,23 @@
       </c>
       <c r="D57" s="2">
         <f>B57+C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2794</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="D58" s="2">
+        <f>B58+C58</f>
         <v/>
       </c>
     </row>
@@ -1980,7 +1997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2960,6 +2977,23 @@
       </c>
       <c r="D57" s="2">
         <f>B57+C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>13556</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>7082</v>
+      </c>
+      <c r="D58" s="2">
+        <f>B58+C58</f>
         <v/>
       </c>
     </row>
@@ -2975,7 +3009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3958,6 +3992,23 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2495</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D58" s="2">
+        <f>B58+C58</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$58</f>
+              <f>'OssDsign'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$58</f>
+              <f>'OssDsign'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$58</f>
+              <f>'OssDsign'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$58</f>
+              <f>'OssDsign'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$58</f>
+              <f>'Smart Eye'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$58</f>
+              <f>'Smart Eye'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$58</f>
+              <f>'Smart Eye'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$58</f>
+              <f>'Smart Eye'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$58</f>
+              <f>'Integrum'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$58</f>
+              <f>'Integrum'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$58</f>
+              <f>'Integrum'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$58</f>
+              <f>'Integrum'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1982,6 +1982,23 @@
       </c>
       <c r="D58" s="2">
         <f>B58+C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2792</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D59" s="2">
+        <f>B59+C59</f>
         <v/>
       </c>
     </row>
@@ -1997,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2994,6 +3011,23 @@
       </c>
       <c r="D58" s="2">
         <f>B58+C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>13555</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>7081</v>
+      </c>
+      <c r="D59" s="2">
+        <f>B59+C59</f>
         <v/>
       </c>
     </row>
@@ -3009,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4009,6 +4043,23 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2492</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D59" s="2">
+        <f>B59+C59</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$59</f>
+              <f>'OssDsign'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$59</f>
+              <f>'OssDsign'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$59</f>
+              <f>'OssDsign'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$59</f>
+              <f>'OssDsign'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$59</f>
+              <f>'Smart Eye'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$59</f>
+              <f>'Smart Eye'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$59</f>
+              <f>'Smart Eye'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$59</f>
+              <f>'Smart Eye'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$59</f>
+              <f>'Integrum'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$59</f>
+              <f>'Integrum'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$59</f>
+              <f>'Integrum'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$59</f>
+              <f>'Integrum'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1999,6 +1999,23 @@
       </c>
       <c r="D59" s="2">
         <f>B59+C59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2788</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D60" s="2">
+        <f>B60+C60</f>
         <v/>
       </c>
     </row>
@@ -2014,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3028,6 +3045,23 @@
       </c>
       <c r="D59" s="2">
         <f>B59+C59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>13526</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>7073</v>
+      </c>
+      <c r="D60" s="2">
+        <f>B60+C60</f>
         <v/>
       </c>
     </row>
@@ -3043,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4060,6 +4094,23 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2491</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D60" s="2">
+        <f>B60+C60</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$60</f>
+              <f>'OssDsign'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$60</f>
+              <f>'OssDsign'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$60</f>
+              <f>'OssDsign'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$60</f>
+              <f>'OssDsign'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$60</f>
+              <f>'Smart Eye'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$60</f>
+              <f>'Smart Eye'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$60</f>
+              <f>'Smart Eye'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$60</f>
+              <f>'Smart Eye'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$60</f>
+              <f>'Integrum'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$60</f>
+              <f>'Integrum'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$60</f>
+              <f>'Integrum'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$60</f>
+              <f>'Integrum'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2016,6 +2016,23 @@
       </c>
       <c r="D60" s="2">
         <f>B60+C60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2783</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D61" s="2">
+        <f>B61+C61</f>
         <v/>
       </c>
     </row>
@@ -2031,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3062,6 +3079,23 @@
       </c>
       <c r="D60" s="2">
         <f>B60+C60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>13506</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>7073</v>
+      </c>
+      <c r="D61" s="2">
+        <f>B61+C61</f>
         <v/>
       </c>
     </row>
@@ -3077,7 +3111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4111,6 +4145,23 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2487</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D61" s="2">
+        <f>B61+C61</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$61</f>
+              <f>'OssDsign'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$61</f>
+              <f>'OssDsign'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$61</f>
+              <f>'OssDsign'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$61</f>
+              <f>'OssDsign'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$61</f>
+              <f>'Smart Eye'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$61</f>
+              <f>'Smart Eye'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$61</f>
+              <f>'Smart Eye'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$61</f>
+              <f>'Smart Eye'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$61</f>
+              <f>'Integrum'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$61</f>
+              <f>'Integrum'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$61</f>
+              <f>'Integrum'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$61</f>
+              <f>'Integrum'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2033,6 +2033,23 @@
       </c>
       <c r="D61" s="2">
         <f>B61+C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2783</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D62" s="2">
+        <f>B62+C62</f>
         <v/>
       </c>
     </row>
@@ -2048,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3096,6 +3113,23 @@
       </c>
       <c r="D61" s="2">
         <f>B61+C61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>13506</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>7073</v>
+      </c>
+      <c r="D62" s="2">
+        <f>B62+C62</f>
         <v/>
       </c>
     </row>
@@ -3111,7 +3145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4162,6 +4196,23 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2487</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D62" s="2">
+        <f>B62+C62</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$62</f>
+              <f>'OssDsign'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$62</f>
+              <f>'OssDsign'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$62</f>
+              <f>'OssDsign'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$62</f>
+              <f>'OssDsign'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$62</f>
+              <f>'Smart Eye'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$62</f>
+              <f>'Smart Eye'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$62</f>
+              <f>'Smart Eye'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$62</f>
+              <f>'Smart Eye'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$62</f>
+              <f>'Integrum'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$62</f>
+              <f>'Integrum'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$62</f>
+              <f>'Integrum'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$62</f>
+              <f>'Integrum'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2050,23 @@
       </c>
       <c r="D62" s="2">
         <f>B62+C62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2783</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D63" s="2">
+        <f>B63+C63</f>
         <v/>
       </c>
     </row>
@@ -2065,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3130,6 +3147,23 @@
       </c>
       <c r="D62" s="2">
         <f>B62+C62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>13506</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>7061</v>
+      </c>
+      <c r="D63" s="2">
+        <f>B63+C63</f>
         <v/>
       </c>
     </row>
@@ -3145,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4213,6 +4247,23 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2487</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D63" s="2">
+        <f>B63+C63</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$63</f>
+              <f>'OssDsign'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$63</f>
+              <f>'OssDsign'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$63</f>
+              <f>'OssDsign'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$63</f>
+              <f>'OssDsign'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$63</f>
+              <f>'Smart Eye'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$63</f>
+              <f>'Smart Eye'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$63</f>
+              <f>'Smart Eye'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$63</f>
+              <f>'Smart Eye'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$63</f>
+              <f>'Integrum'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$63</f>
+              <f>'Integrum'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$63</f>
+              <f>'Integrum'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$63</f>
+              <f>'Integrum'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2067,23 @@
       </c>
       <c r="D63" s="2">
         <f>B63+C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2779</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="D64" s="2">
+        <f>B64+C64</f>
         <v/>
       </c>
     </row>
@@ -2082,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3164,6 +3181,23 @@
       </c>
       <c r="D63" s="2">
         <f>B63+C63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>13488</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>7044</v>
+      </c>
+      <c r="D64" s="2">
+        <f>B64+C64</f>
         <v/>
       </c>
     </row>
@@ -3179,7 +3213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4264,6 +4298,23 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2489</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D64" s="2">
+        <f>B64+C64</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$64</f>
+              <f>'OssDsign'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$64</f>
+              <f>'OssDsign'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$64</f>
+              <f>'OssDsign'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$64</f>
+              <f>'OssDsign'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$64</f>
+              <f>'Smart Eye'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$64</f>
+              <f>'Smart Eye'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$64</f>
+              <f>'Smart Eye'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$64</f>
+              <f>'Smart Eye'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$64</f>
+              <f>'Integrum'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$64</f>
+              <f>'Integrum'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$64</f>
+              <f>'Integrum'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$64</f>
+              <f>'Integrum'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2084,23 @@
       </c>
       <c r="D64" s="2">
         <f>B64+C64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2774</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="D65" s="2">
+        <f>B65+C65</f>
         <v/>
       </c>
     </row>
@@ -2099,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3198,6 +3215,23 @@
       </c>
       <c r="D64" s="2">
         <f>B64+C64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>13442</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>7022</v>
+      </c>
+      <c r="D65" s="2">
+        <f>B65+C65</f>
         <v/>
       </c>
     </row>
@@ -3213,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4315,6 +4349,23 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2486</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D65" s="2">
+        <f>B65+C65</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$65</f>
+              <f>'OssDsign'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$65</f>
+              <f>'OssDsign'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$65</f>
+              <f>'OssDsign'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$65</f>
+              <f>'OssDsign'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$65</f>
+              <f>'Smart Eye'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$65</f>
+              <f>'Smart Eye'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$65</f>
+              <f>'Smart Eye'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$65</f>
+              <f>'Smart Eye'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$65</f>
+              <f>'Integrum'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$65</f>
+              <f>'Integrum'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$65</f>
+              <f>'Integrum'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$65</f>
+              <f>'Integrum'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,23 @@
       </c>
       <c r="D65" s="2">
         <f>B65+C65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2772</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="D66" s="2">
+        <f>B66+C66</f>
         <v/>
       </c>
     </row>
@@ -2116,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3232,6 +3249,23 @@
       </c>
       <c r="D65" s="2">
         <f>B65+C65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>13423</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>7008</v>
+      </c>
+      <c r="D66" s="2">
+        <f>B66+C66</f>
         <v/>
       </c>
     </row>
@@ -3247,7 +3281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4366,6 +4400,23 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D66" s="2">
+        <f>B66+C66</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$66</f>
+              <f>'OssDsign'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$66</f>
+              <f>'OssDsign'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$66</f>
+              <f>'OssDsign'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$66</f>
+              <f>'OssDsign'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$66</f>
+              <f>'Smart Eye'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$66</f>
+              <f>'Smart Eye'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$66</f>
+              <f>'Smart Eye'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$66</f>
+              <f>'Smart Eye'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$66</f>
+              <f>'Integrum'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$66</f>
+              <f>'Integrum'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$66</f>
+              <f>'Integrum'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$66</f>
+              <f>'Integrum'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2118,6 +2118,23 @@
       </c>
       <c r="D66" s="2">
         <f>B66+C66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2772</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="D67" s="2">
+        <f>B67+C67</f>
         <v/>
       </c>
     </row>
@@ -2133,7 +2150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3266,6 +3283,23 @@
       </c>
       <c r="D66" s="2">
         <f>B66+C66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>13404</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="D67" s="2">
+        <f>B67+C67</f>
         <v/>
       </c>
     </row>
@@ -3281,7 +3315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4417,6 +4451,23 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2472</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D67" s="2">
+        <f>B67+C67</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$67</f>
+              <f>'OssDsign'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$67</f>
+              <f>'OssDsign'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$67</f>
+              <f>'OssDsign'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$67</f>
+              <f>'OssDsign'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$67</f>
+              <f>'Smart Eye'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$67</f>
+              <f>'Smart Eye'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$67</f>
+              <f>'Smart Eye'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$67</f>
+              <f>'Smart Eye'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$67</f>
+              <f>'Integrum'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$67</f>
+              <f>'Integrum'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$67</f>
+              <f>'Integrum'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$67</f>
+              <f>'Integrum'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2135,23 @@
       </c>
       <c r="D67" s="2">
         <f>B67+C67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="D68" s="2">
+        <f>B68+C68</f>
         <v/>
       </c>
     </row>
@@ -2150,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3300,6 +3317,23 @@
       </c>
       <c r="D67" s="2">
         <f>B67+C67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>13377</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="D68" s="2">
+        <f>B68+C68</f>
         <v/>
       </c>
     </row>
@@ -3315,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4468,6 +4502,23 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2467</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D68" s="2">
+        <f>B68+C68</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$68</f>
+              <f>'OssDsign'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$68</f>
+              <f>'OssDsign'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$68</f>
+              <f>'OssDsign'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$68</f>
+              <f>'OssDsign'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$68</f>
+              <f>'Smart Eye'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$68</f>
+              <f>'Smart Eye'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$68</f>
+              <f>'Smart Eye'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$68</f>
+              <f>'Smart Eye'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$68</f>
+              <f>'Integrum'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$68</f>
+              <f>'Integrum'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$68</f>
+              <f>'Integrum'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$68</f>
+              <f>'Integrum'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2152,23 @@
       </c>
       <c r="D68" s="2">
         <f>B68+C68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="D69" s="2">
+        <f>B69+C69</f>
         <v/>
       </c>
     </row>
@@ -2167,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3334,6 +3351,23 @@
       </c>
       <c r="D68" s="2">
         <f>B68+C68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>13377</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="D69" s="2">
+        <f>B69+C69</f>
         <v/>
       </c>
     </row>
@@ -3349,7 +3383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4519,6 +4553,23 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2467</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D69" s="2">
+        <f>B69+C69</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$69</f>
+              <f>'OssDsign'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$69</f>
+              <f>'OssDsign'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$69</f>
+              <f>'OssDsign'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$69</f>
+              <f>'OssDsign'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$69</f>
+              <f>'Smart Eye'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$69</f>
+              <f>'Smart Eye'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$69</f>
+              <f>'Smart Eye'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$69</f>
+              <f>'Smart Eye'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$69</f>
+              <f>'Integrum'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$69</f>
+              <f>'Integrum'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$69</f>
+              <f>'Integrum'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$69</f>
+              <f>'Integrum'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2169,23 @@
       </c>
       <c r="D69" s="2">
         <f>B69+C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2768</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="D70" s="2">
+        <f>B70+C70</f>
         <v/>
       </c>
     </row>
@@ -2184,7 +2201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3368,6 +3385,23 @@
       </c>
       <c r="D69" s="2">
         <f>B69+C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>13377</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>6978</v>
+      </c>
+      <c r="D70" s="2">
+        <f>B70+C70</f>
         <v/>
       </c>
     </row>
@@ -3383,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4570,6 +4604,23 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2467</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D70" s="2">
+        <f>B70+C70</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$70</f>
+              <f>'OssDsign'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$70</f>
+              <f>'OssDsign'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$70</f>
+              <f>'OssDsign'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$70</f>
+              <f>'OssDsign'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$70</f>
+              <f>'Smart Eye'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$70</f>
+              <f>'Smart Eye'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$70</f>
+              <f>'Smart Eye'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$70</f>
+              <f>'Smart Eye'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$70</f>
+              <f>'Integrum'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$70</f>
+              <f>'Integrum'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$70</f>
+              <f>'Integrum'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$70</f>
+              <f>'Integrum'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2186,23 @@
       </c>
       <c r="D70" s="2">
         <f>B70+C70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2761</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="D71" s="2">
+        <f>B71+C71</f>
         <v/>
       </c>
     </row>
@@ -2201,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3402,6 +3419,23 @@
       </c>
       <c r="D70" s="2">
         <f>B70+C70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>13375</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>6966</v>
+      </c>
+      <c r="D71" s="2">
+        <f>B71+C71</f>
         <v/>
       </c>
     </row>
@@ -3417,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4621,6 +4655,23 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="D71" s="2">
+        <f>B71+C71</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$71</f>
+              <f>'OssDsign'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$71</f>
+              <f>'OssDsign'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$71</f>
+              <f>'OssDsign'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$71</f>
+              <f>'OssDsign'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$71</f>
+              <f>'Smart Eye'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$71</f>
+              <f>'Smart Eye'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$71</f>
+              <f>'Smart Eye'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$71</f>
+              <f>'Smart Eye'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$71</f>
+              <f>'Integrum'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$71</f>
+              <f>'Integrum'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$71</f>
+              <f>'Integrum'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$71</f>
+              <f>'Integrum'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2203,6 +2203,23 @@
       </c>
       <c r="D71" s="2">
         <f>B71+C71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2758</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="D72" s="2">
+        <f>B72+C72</f>
         <v/>
       </c>
     </row>
@@ -2218,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3436,6 +3453,23 @@
       </c>
       <c r="D71" s="2">
         <f>B71+C71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>13325</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>6949</v>
+      </c>
+      <c r="D72" s="2">
+        <f>B72+C72</f>
         <v/>
       </c>
     </row>
@@ -3451,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4672,6 +4706,23 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2462</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D72" s="2">
+        <f>B72+C72</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$72</f>
+              <f>'OssDsign'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$72</f>
+              <f>'OssDsign'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$72</f>
+              <f>'OssDsign'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$72</f>
+              <f>'OssDsign'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$72</f>
+              <f>'Smart Eye'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$72</f>
+              <f>'Smart Eye'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$72</f>
+              <f>'Smart Eye'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$72</f>
+              <f>'Smart Eye'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$72</f>
+              <f>'Integrum'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$72</f>
+              <f>'Integrum'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$72</f>
+              <f>'Integrum'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$72</f>
+              <f>'Integrum'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2220,6 +2220,23 @@
       </c>
       <c r="D72" s="2">
         <f>B72+C72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2755</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="D73" s="2">
+        <f>B73+C73</f>
         <v/>
       </c>
     </row>
@@ -2235,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3470,6 +3487,23 @@
       </c>
       <c r="D72" s="2">
         <f>B72+C72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>13307</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>6937</v>
+      </c>
+      <c r="D73" s="2">
+        <f>B73+C73</f>
         <v/>
       </c>
     </row>
@@ -3485,7 +3519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4723,6 +4757,23 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2460</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D73" s="2">
+        <f>B73+C73</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$73</f>
+              <f>'OssDsign'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$73</f>
+              <f>'OssDsign'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$73</f>
+              <f>'OssDsign'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$73</f>
+              <f>'OssDsign'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$73</f>
+              <f>'Smart Eye'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$73</f>
+              <f>'Smart Eye'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$73</f>
+              <f>'Smart Eye'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$73</f>
+              <f>'Smart Eye'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$73</f>
+              <f>'Integrum'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$73</f>
+              <f>'Integrum'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$73</f>
+              <f>'Integrum'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$73</f>
+              <f>'Integrum'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2237,23 @@
       </c>
       <c r="D73" s="2">
         <f>B73+C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2751</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="D74" s="2">
+        <f>B74+C74</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3504,6 +3521,23 @@
       </c>
       <c r="D73" s="2">
         <f>B73+C73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>13267</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>6901</v>
+      </c>
+      <c r="D74" s="2">
+        <f>B74+C74</f>
         <v/>
       </c>
     </row>
@@ -3519,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4774,6 +4808,23 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2460</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D74" s="2">
+        <f>B74+C74</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$74</f>
+              <f>'OssDsign'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$74</f>
+              <f>'OssDsign'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$74</f>
+              <f>'OssDsign'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$74</f>
+              <f>'OssDsign'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$74</f>
+              <f>'Smart Eye'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$74</f>
+              <f>'Smart Eye'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$74</f>
+              <f>'Smart Eye'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$74</f>
+              <f>'Smart Eye'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$74</f>
+              <f>'Integrum'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$74</f>
+              <f>'Integrum'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$74</f>
+              <f>'Integrum'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$74</f>
+              <f>'Integrum'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2254,6 +2254,23 @@
       </c>
       <c r="D74" s="2">
         <f>B74+C74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2745</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="D75" s="2">
+        <f>B75+C75</f>
         <v/>
       </c>
     </row>
@@ -2269,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3538,6 +3555,23 @@
       </c>
       <c r="D74" s="2">
         <f>B74+C74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>13242</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>6901</v>
+      </c>
+      <c r="D75" s="2">
+        <f>B75+C75</f>
         <v/>
       </c>
     </row>
@@ -3553,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4825,6 +4859,23 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D75" s="2">
+        <f>B75+C75</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$75</f>
+              <f>'OssDsign'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$75</f>
+              <f>'OssDsign'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$75</f>
+              <f>'OssDsign'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$75</f>
+              <f>'OssDsign'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$75</f>
+              <f>'Smart Eye'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$75</f>
+              <f>'Smart Eye'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$75</f>
+              <f>'Smart Eye'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$75</f>
+              <f>'Smart Eye'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$75</f>
+              <f>'Integrum'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$75</f>
+              <f>'Integrum'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$75</f>
+              <f>'Integrum'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$75</f>
+              <f>'Integrum'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2271,6 +2271,23 @@
       </c>
       <c r="D75" s="2">
         <f>B75+C75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2745</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="D76" s="2">
+        <f>B76+C76</f>
         <v/>
       </c>
     </row>
@@ -2286,7 +2303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3572,6 +3589,23 @@
       </c>
       <c r="D75" s="2">
         <f>B75+C75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>13242</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>6901</v>
+      </c>
+      <c r="D76" s="2">
+        <f>B76+C76</f>
         <v/>
       </c>
     </row>
@@ -3587,7 +3621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4876,6 +4910,23 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D76" s="2">
+        <f>B76+C76</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$76</f>
+              <f>'OssDsign'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$76</f>
+              <f>'OssDsign'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$76</f>
+              <f>'OssDsign'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$76</f>
+              <f>'OssDsign'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$76</f>
+              <f>'Smart Eye'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$76</f>
+              <f>'Smart Eye'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$76</f>
+              <f>'Smart Eye'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$76</f>
+              <f>'Smart Eye'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$76</f>
+              <f>'Integrum'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$76</f>
+              <f>'Integrum'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$76</f>
+              <f>'Integrum'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$76</f>
+              <f>'Integrum'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2288,23 @@
       </c>
       <c r="D76" s="2">
         <f>B76+C76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2745</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="D77" s="2">
+        <f>B77+C77</f>
         <v/>
       </c>
     </row>
@@ -2303,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3606,6 +3623,23 @@
       </c>
       <c r="D76" s="2">
         <f>B76+C76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>13242</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>6887</v>
+      </c>
+      <c r="D77" s="2">
+        <f>B77+C77</f>
         <v/>
       </c>
     </row>
@@ -3621,7 +3655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4927,6 +4961,23 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="D77" s="2">
+        <f>B77+C77</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$77</f>
+              <f>'OssDsign'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$77</f>
+              <f>'OssDsign'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$77</f>
+              <f>'OssDsign'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$77</f>
+              <f>'OssDsign'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$77</f>
+              <f>'Smart Eye'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$77</f>
+              <f>'Smart Eye'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$77</f>
+              <f>'Smart Eye'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$77</f>
+              <f>'Smart Eye'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$77</f>
+              <f>'Integrum'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$77</f>
+              <f>'Integrum'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$77</f>
+              <f>'Integrum'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$77</f>
+              <f>'Integrum'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2305,6 +2305,23 @@
       </c>
       <c r="D77" s="2">
         <f>B77+C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2742</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="D78" s="2">
+        <f>B78+C78</f>
         <v/>
       </c>
     </row>
@@ -2320,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3640,6 +3657,23 @@
       </c>
       <c r="D77" s="2">
         <f>B77+C77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>13226</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>6865</v>
+      </c>
+      <c r="D78" s="2">
+        <f>B78+C78</f>
         <v/>
       </c>
     </row>
@@ -3655,7 +3689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4978,6 +5012,23 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="D78" s="2">
+        <f>B78+C78</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$78</f>
+              <f>'OssDsign'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$78</f>
+              <f>'OssDsign'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$78</f>
+              <f>'OssDsign'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$78</f>
+              <f>'OssDsign'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$78</f>
+              <f>'Smart Eye'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$78</f>
+              <f>'Smart Eye'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$78</f>
+              <f>'Smart Eye'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$78</f>
+              <f>'Smart Eye'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$78</f>
+              <f>'Integrum'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$78</f>
+              <f>'Integrum'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$78</f>
+              <f>'Integrum'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$78</f>
+              <f>'Integrum'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2322,6 +2322,23 @@
       </c>
       <c r="D78" s="2">
         <f>B78+C78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2739</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="D79" s="2">
+        <f>B79+C79</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3674,6 +3691,23 @@
       </c>
       <c r="D78" s="2">
         <f>B78+C78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>13202</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>6837</v>
+      </c>
+      <c r="D79" s="2">
+        <f>B79+C79</f>
         <v/>
       </c>
     </row>
@@ -3689,7 +3723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5029,6 +5063,23 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>558</v>
+      </c>
+      <c r="D79" s="2">
+        <f>B79+C79</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$79</f>
+              <f>'OssDsign'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$79</f>
+              <f>'OssDsign'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$79</f>
+              <f>'OssDsign'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$79</f>
+              <f>'OssDsign'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$79</f>
+              <f>'Smart Eye'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$79</f>
+              <f>'Smart Eye'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$79</f>
+              <f>'Smart Eye'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$79</f>
+              <f>'Smart Eye'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$79</f>
+              <f>'Integrum'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$79</f>
+              <f>'Integrum'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$79</f>
+              <f>'Integrum'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$79</f>
+              <f>'Integrum'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2339,6 +2339,23 @@
       </c>
       <c r="D79" s="2">
         <f>B79+C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2737</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="D80" s="2">
+        <f>B80+C80</f>
         <v/>
       </c>
     </row>
@@ -2354,7 +2371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3708,6 +3725,23 @@
       </c>
       <c r="D79" s="2">
         <f>B79+C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>13176</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>6822</v>
+      </c>
+      <c r="D80" s="2">
+        <f>B80+C80</f>
         <v/>
       </c>
     </row>
@@ -3723,7 +3757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5080,6 +5114,23 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D80" s="2">
+        <f>B80+C80</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$80</f>
+              <f>'OssDsign'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$80</f>
+              <f>'OssDsign'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$80</f>
+              <f>'OssDsign'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$80</f>
+              <f>'OssDsign'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$80</f>
+              <f>'Smart Eye'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$80</f>
+              <f>'Smart Eye'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$80</f>
+              <f>'Smart Eye'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$80</f>
+              <f>'Smart Eye'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$80</f>
+              <f>'Integrum'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$80</f>
+              <f>'Integrum'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$80</f>
+              <f>'Integrum'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$80</f>
+              <f>'Integrum'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2356,6 +2356,23 @@
       </c>
       <c r="D80" s="2">
         <f>B80+C80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2733</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="D81" s="2">
+        <f>B81+C81</f>
         <v/>
       </c>
     </row>
@@ -2371,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3742,6 +3759,23 @@
       </c>
       <c r="D80" s="2">
         <f>B80+C80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>13150</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="D81" s="2">
+        <f>B81+C81</f>
         <v/>
       </c>
     </row>
@@ -3757,7 +3791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5131,6 +5165,23 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2457</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D81" s="2">
+        <f>B81+C81</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$81</f>
+              <f>'OssDsign'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$81</f>
+              <f>'OssDsign'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$81</f>
+              <f>'OssDsign'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$81</f>
+              <f>'OssDsign'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$81</f>
+              <f>'Smart Eye'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$81</f>
+              <f>'Smart Eye'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$81</f>
+              <f>'Smart Eye'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$81</f>
+              <f>'Smart Eye'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$81</f>
+              <f>'Integrum'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$81</f>
+              <f>'Integrum'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$81</f>
+              <f>'Integrum'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$81</f>
+              <f>'Integrum'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2373,6 +2373,23 @@
       </c>
       <c r="D81" s="2">
         <f>B81+C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2729</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="D82" s="2">
+        <f>B82+C82</f>
         <v/>
       </c>
     </row>
@@ -2388,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3776,6 +3793,23 @@
       </c>
       <c r="D81" s="2">
         <f>B81+C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>13132</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="D82" s="2">
+        <f>B82+C82</f>
         <v/>
       </c>
     </row>
@@ -3791,7 +3825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5182,6 +5216,23 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D82" s="2">
+        <f>B82+C82</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$82</f>
+              <f>'OssDsign'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$82</f>
+              <f>'OssDsign'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$82</f>
+              <f>'OssDsign'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$82</f>
+              <f>'OssDsign'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +349,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$82</f>
+              <f>'Smart Eye'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$82</f>
+              <f>'Smart Eye'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$82</f>
+              <f>'Smart Eye'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$82</f>
+              <f>'Smart Eye'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$82</f>
+              <f>'Integrum'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$82</f>
+              <f>'Integrum'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$82</f>
+              <f>'Integrum'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$82</f>
+              <f>'Integrum'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2390,6 +2390,23 @@
       </c>
       <c r="D82" s="2">
         <f>B82+C82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2729</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="D83" s="2">
+        <f>B83+C83</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3810,6 +3827,23 @@
       </c>
       <c r="D82" s="2">
         <f>B82+C82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>13132</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="D83" s="2">
+        <f>B83+C83</f>
         <v/>
       </c>
     </row>
@@ -3825,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5233,6 +5267,23 @@
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="D83" s="2">
+        <f>B83+C83</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -10,6 +10,7 @@
     <sheet name="OssDsign" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Smart Eye" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Integrum" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Green Landscaping" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$83</f>
+              <f>'OssDsign'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$83</f>
+              <f>'OssDsign'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$83</f>
+              <f>'OssDsign'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$83</f>
+              <f>'OssDsign'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -349,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$83</f>
+              <f>'Smart Eye'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$83</f>
+              <f>'Smart Eye'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$83</f>
+              <f>'Smart Eye'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$83</f>
+              <f>'Smart Eye'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -506,12 +507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$83</f>
+              <f>'Integrum'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$83</f>
+              <f>'Integrum'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +542,169 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$83</f>
+              <f>'Integrum'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$83</f>
+              <f>'Integrum'!$C$2:$C$84</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Datum</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Antal ägare</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Green Landscaping – antal ägare över tid</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Green Landscaping'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF3B30"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Green Landscaping'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Green Landscaping'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Green Landscaping'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="34C9EB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Green Landscaping'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Green Landscaping'!$C$2</f>
             </numRef>
           </val>
         </ser>
@@ -670,6 +828,33 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -985,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2407,6 +2592,23 @@
       </c>
       <c r="D83" s="2">
         <f>B83+C83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2729</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D84" s="2">
+        <f>B84+C84</f>
         <v/>
       </c>
     </row>
@@ -2422,7 +2624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3844,6 +4046,23 @@
       </c>
       <c r="D83" s="2">
         <f>B83+C83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>13132</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>6794</v>
+      </c>
+      <c r="D84" s="2">
+        <f>B84+C84</f>
         <v/>
       </c>
     </row>
@@ -3859,7 +4078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5284,6 +5503,83 @@
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="D84" s="2">
+        <f>B84+C84</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avanza</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nordnet</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Totalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2514</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="D2" s="2">
+        <f>B2+C2</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$84</f>
+              <f>'OssDsign'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$84</f>
+              <f>'OssDsign'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$84</f>
+              <f>'OssDsign'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$84</f>
+              <f>'OssDsign'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$84</f>
+              <f>'Smart Eye'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$84</f>
+              <f>'Smart Eye'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$84</f>
+              <f>'Smart Eye'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$84</f>
+              <f>'Smart Eye'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$84</f>
+              <f>'Integrum'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$84</f>
+              <f>'Integrum'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -542,12 +542,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$84</f>
+              <f>'Integrum'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$84</f>
+              <f>'Integrum'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -664,12 +664,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2</f>
+              <f>'Green Landscaping'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$B$2</f>
+              <f>'Green Landscaping'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -699,12 +699,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2</f>
+              <f>'Green Landscaping'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$C$2</f>
+              <f>'Green Landscaping'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2609,6 +2609,23 @@
       </c>
       <c r="D84" s="2">
         <f>B84+C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2732</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D85" s="2">
+        <f>B85+C85</f>
         <v/>
       </c>
     </row>
@@ -2624,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4063,6 +4080,23 @@
       </c>
       <c r="D84" s="2">
         <f>B84+C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>13117</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>6784</v>
+      </c>
+      <c r="D85" s="2">
+        <f>B85+C85</f>
         <v/>
       </c>
     </row>
@@ -4078,7 +4112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5517,6 +5551,23 @@
       </c>
       <c r="D84" s="2">
         <f>B84+C84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2451</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="D85" s="2">
+        <f>B85+C85</f>
         <v/>
       </c>
     </row>
@@ -5532,7 +5583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5580,6 +5631,23 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2525</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3+C3</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$85</f>
+              <f>'OssDsign'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$85</f>
+              <f>'OssDsign'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$85</f>
+              <f>'OssDsign'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$85</f>
+              <f>'OssDsign'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$85</f>
+              <f>'Smart Eye'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$85</f>
+              <f>'Smart Eye'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$85</f>
+              <f>'Smart Eye'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$85</f>
+              <f>'Smart Eye'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$85</f>
+              <f>'Integrum'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$85</f>
+              <f>'Integrum'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -542,12 +542,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$85</f>
+              <f>'Integrum'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$85</f>
+              <f>'Integrum'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -664,12 +664,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$3</f>
+              <f>'Green Landscaping'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$B$2:$B$3</f>
+              <f>'Green Landscaping'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -699,12 +699,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$3</f>
+              <f>'Green Landscaping'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$C$2:$C$3</f>
+              <f>'Green Landscaping'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2626,6 +2626,23 @@
       </c>
       <c r="D85" s="2">
         <f>B85+C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2725</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D86" s="2">
+        <f>B86+C86</f>
         <v/>
       </c>
     </row>
@@ -2641,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4097,6 +4114,23 @@
       </c>
       <c r="D85" s="2">
         <f>B85+C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>13096</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>6770</v>
+      </c>
+      <c r="D86" s="2">
+        <f>B86+C86</f>
         <v/>
       </c>
     </row>
@@ -4112,7 +4146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5568,6 +5602,23 @@
       </c>
       <c r="D85" s="2">
         <f>B85+C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2451</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="D86" s="2">
+        <f>B86+C86</f>
         <v/>
       </c>
     </row>
@@ -5583,7 +5634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5648,6 +5699,23 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2524</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4+C4</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$86</f>
+              <f>'OssDsign'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$86</f>
+              <f>'OssDsign'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$86</f>
+              <f>'OssDsign'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$86</f>
+              <f>'OssDsign'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$86</f>
+              <f>'Smart Eye'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$86</f>
+              <f>'Smart Eye'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$86</f>
+              <f>'Smart Eye'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$86</f>
+              <f>'Smart Eye'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$86</f>
+              <f>'Integrum'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$86</f>
+              <f>'Integrum'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -542,12 +542,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$86</f>
+              <f>'Integrum'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$86</f>
+              <f>'Integrum'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -664,12 +664,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$4</f>
+              <f>'Green Landscaping'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$B$2:$B$4</f>
+              <f>'Green Landscaping'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -699,12 +699,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$4</f>
+              <f>'Green Landscaping'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$C$2:$C$4</f>
+              <f>'Green Landscaping'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2643,6 +2643,23 @@
       </c>
       <c r="D86" s="2">
         <f>B86+C86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2718</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="D87" s="2">
+        <f>B87+C87</f>
         <v/>
       </c>
     </row>
@@ -2658,7 +2675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4131,6 +4148,23 @@
       </c>
       <c r="D86" s="2">
         <f>B86+C86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>13061</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>6763</v>
+      </c>
+      <c r="D87" s="2">
+        <f>B87+C87</f>
         <v/>
       </c>
     </row>
@@ -4146,7 +4180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5619,6 +5653,23 @@
       </c>
       <c r="D86" s="2">
         <f>B86+C86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2449</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="D87" s="2">
+        <f>B87+C87</f>
         <v/>
       </c>
     </row>
@@ -5634,7 +5685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5716,6 +5767,23 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2522</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5+C5</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/data/agartracker.xlsx
+++ b/data/agartracker.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$87</f>
+              <f>'OssDsign'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$B$2:$B$87</f>
+              <f>'OssDsign'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'OssDsign'!$A$2:$A$87</f>
+              <f>'OssDsign'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'OssDsign'!$C$2:$C$87</f>
+              <f>'OssDsign'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$87</f>
+              <f>'Smart Eye'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$B$2:$B$87</f>
+              <f>'Smart Eye'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Smart Eye'!$A$2:$A$87</f>
+              <f>'Smart Eye'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Smart Eye'!$C$2:$C$87</f>
+              <f>'Smart Eye'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$87</f>
+              <f>'Integrum'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$B$2:$B$87</f>
+              <f>'Integrum'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -542,12 +542,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Integrum'!$A$2:$A$87</f>
+              <f>'Integrum'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Integrum'!$C$2:$C$87</f>
+              <f>'Integrum'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -664,12 +664,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$5</f>
+              <f>'Green Landscaping'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$B$2:$B$5</f>
+              <f>'Green Landscaping'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -699,12 +699,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Green Landscaping'!$A$2:$A$5</f>
+              <f>'Green Landscaping'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Green Landscaping'!$C$2:$C$5</f>
+              <f>'Green Landscaping'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2660,6 +2660,23 @@
       </c>
       <c r="D87" s="2">
         <f>B87+C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2710</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="D88" s="2">
+        <f>B88+C88</f>
         <v/>
       </c>
     </row>
@@ -2675,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4165,6 +4182,23 @@
       </c>
       <c r="D87" s="2">
         <f>B87+C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>13073</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>6766</v>
+      </c>
+      <c r="D88" s="2">
+        <f>B88+C88</f>
         <v/>
       </c>
     </row>
@@ -4180,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5670,6 +5704,23 @@
       </c>
       <c r="D87" s="2">
         <f>B87+C87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2447</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="D88" s="2">
+        <f>B88+C88</f>
         <v/>
       </c>
     </row>
@@ -5685,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5784,6 +5835,23 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2519</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6+C6</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
